--- a/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/recht/Betriebsklar-Nachpruefliste-Rechtsanwalt.xlsx
+++ b/docs/freigabe-katalog/versand-2026-10-25-nachpruefung/recht/Betriebsklar-Nachpruefliste-Rechtsanwalt.xlsx
@@ -496,7 +496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>• Vorlage: Inhalt seit Ihrer Freigabe geändert und/oder ohne unterschriebenes Blatt. Die Prüfsumme bestimmt die Fassung; jede Änderung ergibt eine neue.</t>
+          <t>• Vorlage: ohne unterschriebenes Blatt und/oder eine Variante (Rechtsform, Land, Rechnungsart …) seit Ihrer Freigabe geändert. Je Variante bestimmt eine Prüfsumme die Fassung; eine Änderung betrifft nur ihre Variante.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu den Vorlagen liegen die aktuellen PDFs bei.</t>
+          <t>Am Ende das Blatt „Unterschrift“ ausfüllen und unterschreiben (Scan genügt). Zu geänderten Varianten von Vorlagen liegen PDFs bei (Ordner „vorlagen“).</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>ebc761fd0b5e</t>
+          <t>e1cf092f9b77</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung e10ca1471d30 (bisherige Rechnung 101632b4de7a), heute ebc761fd0b5e. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 (2026-10-25-runde4-recht-mail.txt) nennt ein unterschriebenes Bestätigungsblatt als Anlage; es liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „Länderzusatz nur für Bayern geprüft“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 25.10.2026 (2026-10-25-runde4-recht-mail.txt) nennt ein unterschriebenes Bestätigungsblatt als Anlage; es liegt uns nicht vor). Der Vermerk nennt Ihre Einschränkung: „Länderzusatz nur für Bayern geprüft“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>ef332c109c63</t>
+          <t>c5d2853a2c80</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung bd9056f9f642 (bisherige Rechnung 524dfef7fee9), heute ef332c109c63. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>b263b7f23fdf</t>
+          <t>a93921de34f2</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 8aea7f29b7cd (bisherige Rechnung 1b191e907794), heute b263b7f23fdf. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Die Vorlage enthält 1 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>9dd3d7726bff</t>
+          <t>811a35c4f672</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 97f919eb78c8 (bisherige Rechnung d4a5c4808805), heute 9dd3d7726bff. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>96a909049fe9</t>
+          <t>a02e07c89bf6</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 07949652223e (bisherige Rechnung 5f243298c366), heute 96a909049fe9. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7c32e49d44d2</t>
+          <t>4f7e8ca8b18d</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 51717940123a (bisherige Rechnung e907682096ea), heute 7c32e49d44d2. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>98a813f9749c</t>
+          <t>a6bfb823f90b</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 591895b30f52 (bisherige Rechnung 9d1a06fbb30f), heute 98a813f9749c. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Die Vorlage enthält 2 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Die Vorlage enthält 2 Stelle(n) mit „fachlich zu prüfen“ – bis zur Klärung zeigt die App nur „teilweise durchgesehen“. Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2d730536e3e9</t>
+          <t>ad558f108ab1</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung d6eaf4d003bf (bisherige Rechnung 16515a705e31), heute 2d730536e3e9. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7fbea0d59835</t>
+          <t>3006e5c133a4</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung f595ed34815d (bisherige Rechnung 62df8ed29e69), heute 7fbea0d59835. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>786a61b2bf79</t>
+          <t>f6130d2b1c65</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 81f5c8b34158 (bisherige Rechnung c37a8792a998), heute 786a61b2bf79. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>bf68ccd8d7cf</t>
+          <t>a0ce2389b3cb</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 6c9a0c678006 (bisherige Rechnung 2353e20c509a), heute bf68ccd8d7cf. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6662fe8a68f6</t>
+          <t>a8d0aaca445b</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 59e5262c0240 (bisherige Rechnung 235a53669349), heute 6662fe8a68f6. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>02f1b8b8dcde</t>
+          <t>3951cb4e226f</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 03d4fa91feb6 (bisherige Rechnung 2399c8cf81e2), heute 02f1b8b8dcde. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3e0a093e22f6</t>
+          <t>407eef48f7ba</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 03f2ec23647d (bisherige Rechnung 9e79f2037661), heute 3e0a093e22f6. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>4aef59dbfd22</t>
+          <t>2967ec09f195</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 521a82cc4731 (bisherige Rechnung 8324d37f9471), heute 4aef59dbfd22. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>f8e691f3db04</t>
+          <t>3b0b44db4548</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Seit Ihrer Freigabe geändert: die Fußzeile bei GmbH &amp; Co. KG und UG (haftungsbeschränkt) &amp; Co. KG (Zeile „Persönlich haftende Gesellschafterin: …“ mit den Angaben der Komplementärin, E-193). Prüfsumme der freigegebenen Fassung 1b4287730201 (bisherige Rechnung 01473dc8aef5), heute f8e691f3db04. Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Mail 23.10.2026 (2026-10-23-nachpruefung-vorlagen-recht-mail.txt) kündigt das unterschriebene Bestätigungsblatt an; es liegt uns nicht vor). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>87a97718061f</t>
+          <t>615ef77b91ab</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Bestätigung per Mail ohne unterschriebenes Blatt). Bitte die heutige Fassung (Prüfsumme rechts) durchsehen und bestätigen.</t>
+          <t>Ein unterschriebenes Blatt liegt uns nicht vor (Bestätigung per Mail ohne unterschriebenes Blatt). Inhalt seit Ihrer Freigabe unverändert – bitte nur die Freigabe mit Unterschrift bestätigen.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
